--- a/data/reports/liquidity_report_2025-12-01_full.xlsx
+++ b/data/reports/liquidity_report_2025-12-01_full.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Сформировано: 08.05.2026 18:27 | Единица измерения: руб.</t>
+          <t>Сформировано: 08.05.2026 19:15 | Единица измерения: руб.</t>
         </is>
       </c>
     </row>
@@ -608,16 +608,16 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1700000000</v>
+        <v>5100000000</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>1880000000</v>
+        <v>5640000000</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>-180000000</v>
+        <v>-540000000</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-180000000</v>
+        <v>-540000000</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>-0.09574500000000001</v>
@@ -640,16 +640,16 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>400000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>400000000</v>
+        <v>1200000000</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>220000000</v>
+        <v>660000000</v>
       </c>
       <c r="G5" s="11" t="n">
         <v/>
@@ -672,16 +672,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>300000000</v>
+        <v>900000000</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>600000000</v>
+        <v>1800000000</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>-300000000</v>
+        <v>-900000000</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-80000000</v>
+        <v>-240000000</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>-0.5</v>
@@ -704,16 +704,16 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>960000000</v>
+        <v>2880000000</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-40000000</v>
+        <v>-120000000</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-120000000</v>
+        <v>-360000000</v>
       </c>
       <c r="G7" s="11" t="n">
         <v>-0.04</v>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1500000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>7660000000</v>
+        <v>22980000000</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-6160000000</v>
+        <v>-18480000000</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-6280000000</v>
+        <v>-18840000000</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>-0.8041779999999999</v>
@@ -768,16 +768,16 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>46015000000</v>
+        <v>138045000000</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1200000000</v>
+        <v>3600000000</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>44815000000</v>
+        <v>134445000000</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>38535000000</v>
+        <v>115605000000</v>
       </c>
       <c r="G9" s="11" t="n">
         <v>37.345833</v>
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>960000000</v>
+        <v>2880000000</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>38220000000</v>
+        <v>114660000000</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>-37260000000</v>
+        <v>-111780000000</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1275000000</v>
+        <v>3825000000</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>-0.974882</v>
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>5400000000</v>
+        <v>16200000000</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>2400000000</v>
+        <v>7200000000</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3675000000</v>
+        <v>11025000000</v>
       </c>
       <c r="G11" s="11" t="n">
         <v>0.8</v>
@@ -860,13 +860,13 @@
       </c>
       <c r="B12" s="13" t="n"/>
       <c r="C12" s="14" t="n">
-        <v>57235000000</v>
+        <v>171705000000</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>53560000000</v>
+        <v>160680000000</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>3675000000</v>
+        <v>11025000000</v>
       </c>
       <c r="F12" s="13" t="n"/>
       <c r="G12" s="13" t="n"/>
@@ -911,7 +911,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Сформировано: 08.05.2026 18:27 | Топ контрагентов по доле в портфеле</t>
+          <t>Сформировано: 08.05.2026 19:15 | Топ контрагентов по доле в портфеле</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>45015000000</v>
+        <v>135045000000</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>0.78649</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="E5" s="10" t="n">
-        <v>2000000000</v>
+        <v>6000000000</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>0.03494</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1900000000</v>
+        <v>5700000000</v>
       </c>
       <c r="F6" s="15" t="n">
         <v>0.0332</v>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1700000000</v>
+        <v>5100000000</v>
       </c>
       <c r="F7" s="17" t="n">
         <v>0.0297</v>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1500000000</v>
+        <v>4500000000</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.02621</v>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="F9" s="17" t="n">
         <v>0.01747</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="F10" s="15" t="n">
         <v>0.01747</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>600000000</v>
+        <v>1800000000</v>
       </c>
       <c r="F11" s="17" t="n">
         <v>0.01048</v>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>600000000</v>
+        <v>1800000000</v>
       </c>
       <c r="F12" s="15" t="n">
         <v>0.01048</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="E13" s="10" t="n">
-        <v>500000000</v>
+        <v>1500000000</v>
       </c>
       <c r="F13" s="17" t="n">
         <v>0.00874</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>400000000</v>
+        <v>1200000000</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0.00699</v>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>360000000</v>
+        <v>1080000000</v>
       </c>
       <c r="F15" s="17" t="n">
         <v>0.00629</v>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>300000000</v>
+        <v>900000000</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0.00524</v>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="E17" s="10" t="n">
-        <v>200000000</v>
+        <v>600000000</v>
       </c>
       <c r="F17" s="17" t="n">
         <v>0.00349</v>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>160000000</v>
+        <v>480000000</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0.0028</v>
@@ -1503,7 +1503,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Сформировано: 08.05.2026 18:27 | Топ контрагентов по доле в портфеле</t>
+          <t>Сформировано: 08.05.2026 19:15 | Топ контрагентов по доле в портфеле</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>38220000000</v>
+        <v>114660000000</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>0.7135899999999999</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="E5" s="10" t="n">
-        <v>6300000000</v>
+        <v>18900000000</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>0.11763</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="F6" s="15" t="n">
         <v>0.05601</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1200000000</v>
+        <v>3600000000</v>
       </c>
       <c r="F7" s="17" t="n">
         <v>0.0224</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.01867</v>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>900000000</v>
+        <v>2700000000</v>
       </c>
       <c r="F9" s="17" t="n">
         <v>0.0168</v>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>800000000</v>
+        <v>2400000000</v>
       </c>
       <c r="F10" s="15" t="n">
         <v>0.01494</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>600000000</v>
+        <v>1800000000</v>
       </c>
       <c r="F11" s="17" t="n">
         <v>0.0112</v>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>500000000</v>
+        <v>1500000000</v>
       </c>
       <c r="F12" s="15" t="n">
         <v>0.009340000000000001</v>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="E13" s="10" t="n">
-        <v>400000000</v>
+        <v>1200000000</v>
       </c>
       <c r="F13" s="17" t="n">
         <v>0.00747</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>360000000</v>
+        <v>1080000000</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0.00672</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>160000000</v>
+        <v>480000000</v>
       </c>
       <c r="F15" s="17" t="n">
         <v>0.00299</v>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>120000000</v>
+        <v>360000000</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0.00224</v>
